--- a/datasets/cluster_info.xlsx
+++ b/datasets/cluster_info.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-16 12:27:23</t>
+          <t>2026-06-16 16:32:51</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-16 12:27:23</t>
+          <t>2026-06-16 16:32:51</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-16 12:27:23</t>
+          <t>2026-06-16 16:32:51</t>
         </is>
       </c>
     </row>
